--- a/English/语法.xlsx
+++ b/English/语法.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\web\Englidh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CC6959-A7E0-4E3D-AAD4-9F351DBE1C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412353CD-D85E-46C0-8EFC-57FCAC1638F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>名词</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,6 +204,38 @@
   </si>
   <si>
     <t>Dayan is blaming me for my carelessness.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 主动被动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动语态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动语态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主语是动作发出者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主语是动作承受者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动语态的核心结构是be + 动词过去分词(done)，表达某事/物被执行的动作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这座桥是由政府建造的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The bridge was built by the government</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -211,7 +243,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +274,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -263,10 +303,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -294,8 +335,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>27709</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>273894</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>113190</xdr:rowOff>
     </xdr:to>
@@ -679,8 +720,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A7C180-FD00-4E0F-B89C-A62A7C6144AC}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -788,9 +832,43 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/English/语法.xlsx
+++ b/English/语法.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Reading\Study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412353CD-D85E-46C0-8EFC-57FCAC1638F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37F5F39-9C36-4B0C-B3E3-37E445139573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2235" yWindow="3165" windowWidth="13335" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="词法加句法" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>名词</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -236,6 +234,170 @@
   </si>
   <si>
     <t>The bridge was built by the government</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个勤奋的学生很快理解了这个复杂的概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>The</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> diligent student quickly understood the complicated concept</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周末我有一些家庭作业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have a lot of homework in this weekend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>她未来想做一名工程师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>She</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> wents to become an engineer in the future</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>他给了我一条好建议</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He gave me a piece of good advace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>他掉了一颗牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He lost a tooth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们需要更多关于这件事的信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We need more information about this event</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄们拯救了城市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The heroes saved the city.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是一个关于农夫与蛇的故事</t>
+  </si>
+  <si>
+    <t>This is a story about a farmer and a snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自行车是重要的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The bicycle is important</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我房间里有很多设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have much equipment in my room</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空气和水很重要</t>
+  </si>
+  <si>
+    <t>Air and water are important</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我去过长城两次</t>
+  </si>
+  <si>
+    <t>I have been to Great Wall twice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我喜欢吃苹果和面包</t>
+  </si>
+  <si>
+    <t>I like cating apples and bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a piece 是量词，量词与名词之间必须加 of</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个学生在图书馆借了三本书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The student borrowed three books form the library</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请把水递给我</t>
+  </si>
+  <si>
+    <t>Please pass me the water</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们有土豆和番茄</t>
+  </si>
+  <si>
+    <t>We have potatoes and tomatoes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孩子们在公园玩耍</t>
+  </si>
+  <si>
+    <t>the children playing in the park</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我每天练习英语30分钟</t>
+  </si>
+  <si>
+    <t>I practice English for 30 minutes every day.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -243,17 +405,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -262,7 +424,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -270,17 +432,24 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -303,14 +472,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -637,10 +807,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C79"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -712,18 +882,202 @@
         <v>15</v>
       </c>
     </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A7C180-FD00-4E0F-B89C-A62A7C6144AC}">
   <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">

--- a/English/语法.xlsx
+++ b/English/语法.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Reading\Study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37F5F39-9C36-4B0C-B3E3-37E445139573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C0D2E2-94E5-4014-95BF-C36F646E122F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="3165" windowWidth="13335" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14340" yWindow="6015" windowWidth="11925" windowHeight="9525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="词法加句法" sheetId="1" r:id="rId1"/>
@@ -35,20 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="157">
   <si>
     <t>名词</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I have a lot of homeworks to do this weekend.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>She wants to become engineer in the future</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可数名词不能单独使用 要么加 a/an/The/+s</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -57,47 +49,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>homework</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>an engineer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>He gave me a good advice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>He lost a teeth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>We need more informations about this event</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>The heros saved the city</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a piece of good advice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a tooth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>information</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>heroes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>复数 - O结尾 有生命加 es 没有生命加 s</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -400,12 +352,373 @@
     <t>I practice English for 30 minutes every day.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>The student borrowed three books from the library</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We have potatoes and tomamtoes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The chliden are playing in the park</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I practice English for 30 minutes every day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单数使用名词的原形，复数通常在词尾加 -s / -es</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 可数名词单数：必须有冠词或其他限定词（如this，my）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I need a book to read during the trip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The book you lent me is fascinating</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>原则：若泛指</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"一个",用 a / an修饰名词、若特指“这个/那个”,则使用the</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>冠词勿用：冠词只有</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> a/an/the</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 可数名词复数和不可数名词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解释：可数名词复数和不可数名词的情况一致、当泛指一类事物或不确定范围时、省略冠词，当特指某些事物或特定范围时、则使用the</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变化类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元音变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单复同形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>man</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>woman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tooth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aircraft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>men</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>women</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>teeth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常考名词复数的不规则变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常考不可数名词一览</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>news</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weather</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>air</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knowledge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>traffic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>money</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equipment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>furniture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>experience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用法说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>典型事例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必须使用定冠词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>独一无二的事物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>the moon 、the sun、the earth\the Great Wall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上文提到的事物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>My father tells me  a new story. The story is very funny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>演奏西洋乐器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>play the piano\play the violin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序数词和最高级前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>the frist\the best student</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主谓一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谓语动词的形式必须与其主语在人称和数上保持严格对应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当主语为单数时，谓语必须用单数形式（通常为动词原形加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-s或-es)当主语为复数时、谓语也必须用复数形式（动词原形）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We usually have meetings on Monday morings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He usually has meetings on Monday morings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>These birds fly south for winter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The bird flies south for winter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We don't have enough time to finish everything today</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He doesn't has enough time to finish everyting today</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A number of apps on m phone are useless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 近水楼台的就近原则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谓语单复数往往与离它最近的名词保持一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时态一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当主语不是第三人称单数的时候，谓语动词应使用原形，当主语为第三人称单数（he / she /it /Dayan）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a. 绝大多数动词直接加 -s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b. 以 s x ch sh o结尾的动词加 es</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c. 辅音字母加 y 结尾的动词，变y为i再加es</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. The earth revolves around the sun.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Shanghai lies in the east of China.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Dayan drinks a cup of coffee every day.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Custom makes all things easy.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表示过去某个时间点/段中发生的事情或存在的状态，无论主语单复数，谓语动词都需要使用动词过去湿（通常为动词原形加ed/d形式，部分过去式存在不规则变化）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Dayan drank a cup of coffee yesterday.</t>
+  </si>
+  <si>
+    <t>2. He finally changed his mind yesterday.</t>
+  </si>
+  <si>
+    <t>3. I was a student in 2022.</t>
+  </si>
+  <si>
+    <t>3. They were busy with their final exams two months ago.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,16 +764,55 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -468,16 +820,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -807,265 +1229,632 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="35" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    <row r="38" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="41" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+    <row r="44" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+    <row r="47" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
+    <row r="50" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+    <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="56" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="59" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="62" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="65" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="68" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A67" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A70" s="4" t="s">
+    <row r="70" spans="1:5" ht="21.75" x14ac:dyDescent="0.4">
+      <c r="A70" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="72" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A73" s="4" t="s">
+    <row r="74" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A76" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="77" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
+    <row r="78" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
         <v>86</v>
       </c>
     </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C80" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+    </row>
+    <row r="81" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C81" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C82" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C83" s="10"/>
+      <c r="D83" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C84" s="10"/>
+      <c r="D84" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C85" s="11"/>
+      <c r="D85" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C86" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C87" s="10"/>
+      <c r="D87" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C88" s="11"/>
+      <c r="D88" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C90" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+    </row>
+    <row r="91" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C91" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="92" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C92" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C93" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C94" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C96" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C97" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C98" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C99" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C100" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A105" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="C86:C88"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1082,147 +1871,147 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C35" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C40" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C41" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/English/语法.xlsx
+++ b/English/语法.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Reading\Study\Study\English\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C0D2E2-94E5-4014-95BF-C36F646E122F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D77BDF7-99C8-4EAD-9EDA-77C100802449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="6015" windowWidth="11925" windowHeight="9525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="词法加句法" sheetId="1" r:id="rId1"/>
     <sheet name="时态" sheetId="2" r:id="rId2"/>
+    <sheet name="语法总结" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="217">
   <si>
     <t>名词</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -713,22 +714,262 @@
   <si>
     <t>3. They were busy with their final exams two months ago.</t>
   </si>
+  <si>
+    <t>动词必会核心考点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必会1：主谓一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）语法一致的硬规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法一致要求谓语动词单复数形式严格遵循主语的单复数形式：当主语为单数时，谓语须用单数形式（通常为动词原形加 -s 或 -es)当主语为复数时，谓语也须用复数形式（动词原形）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We usually have meetings on Monday mornings.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He usually has meetings on Monday mornings.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>These birds fly south for winter.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The bird flies south for winter.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We don't have enough time to finish everything today.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He doesn't have enough time to finish everything today.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bread and milk are my favorite breakfast.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Everybody is excited for our class trip.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A number of apps on my phone are useless.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A number of + 复数名词 + 复数谓语  许多…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The number of + 复数名词 + 单数谓语  意为 …的数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法一致原则口诀：单主单谓、复主复谓，不定代词用单谓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2）近水楼台的就近原则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a. 主语由 either … or … / neither … nor … / not noly … but also … / or “四剑客”连接时，谓语动词与它最近的名词保持一致。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neither the manager nor the employee speak Chinese.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Either the phone or the laptop needs repair.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not only my sister but also her friends like this movie.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Your parents or your brother has to clean the room.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b. There be 句型中，谓语动词与离它最近的名词保持一致。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>There is a book and three pens on the desk.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>There are two cats and a dog in the yard.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必会2：时态一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般现在时表示现在发生的习惯、常态、能力或客观事实，通常见到every day / always / sometimes等表示时间的词语，就可以判定句子用一般现在时。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当主语不是第三人称单数时，谓语动词应使用原形，当主语为第三人称单数时，谓语变化如下：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a. 绝大多数动词后直接加 -s (work -&gt; works)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b. 以 s x ch sh o 结尾的动词加 -es (go - goes)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c. 辅音字母加 y 结尾的动词，变 y 为 i再加-es(study -&gt; studies)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dayan drink a cup of coffee every day.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般过去表示过去某个时间点/段中发生的事情或存在的状态，无论主语单复数，谓语动词都需要使用动词过去式（动词原形加 -ed / -d形式，部分动词过去式存在不规则变化）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通常last year / yesterday / ago等表示过去时间的语句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dayan drank a cup of coffee yesterday.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He finally changed his mind yeasterday.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was a student in 2022.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They were busy with their final exams two months ago.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在完成时表示过去发生的某一动作对现在造成的影响或结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要准确构造现在完成时，必须掌握其核心结构 have / has + done(动词的过去分词）。其中，过去分词done 必须与have / has 搭配才能构造完整的谓语部分，绝不能单独出现。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have lost my keys!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He has lived here for ten years.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dayan has already drunk her coffee.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般将来时表示未来将发生的动作或状态。当句子中出现时间标志 tomorrow / next / soon 等词时、就是使用将来时的信号。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两种形式：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) will + 动词原形：表临时决定 或 主观预测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2) be going to + 动词原形： 表已有计划 或 有迹象表明即将发生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当主语人称的单复数产生变化时，be going to 结构中的be动词需要相应变形（I am/you are / he is )，而will结构则不需要改变，两者后面的谓语都必须使用动词原形。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dayan will drink a cup of coffee. 临时决定去喝咖啡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dayan is going to drink a cup of coffee. 已有计划将去喝咖啡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They will study abroad next year.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They are going to study abroad next year.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在进行时表示 “此刻正在发生”的动作或状态，当句子中出现时间标志 now / right now / at the moment等词时，就是使用现在进行时的信号。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定结构为 be + doing ， be动词是该结构的核心，须根据主语的人称和单复数进行变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dayan is drinking a cup of coffee now. (现在的动作）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They are having lunch at the moment. （现在的动作）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The child is being quiet. （现在的状态)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dayan blamed me yesterday because of my carelessness.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dayan will blame me soon.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必会3：主动/被动语态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -737,7 +978,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -745,14 +986,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -775,7 +1016,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -792,9 +1033,16 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="1"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -876,7 +1124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -886,6 +1134,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -895,14 +1147,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1230,18 +1479,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E144"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1249,77 +1498,77 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15.6">
       <c r="A4" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="15.6">
       <c r="A6" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="15.6">
       <c r="A8" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="15.6">
       <c r="A10" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="15.6">
       <c r="A12" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="15.6">
       <c r="A14" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="15.6">
       <c r="A17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="15.6">
       <c r="A19" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="15.6">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="15.6">
       <c r="A23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="15.6">
       <c r="A26" s="4" t="s">
         <v>45</v>
       </c>
@@ -1327,189 +1576,189 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="15.6">
       <c r="A29" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="15.6">
       <c r="A32" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" ht="15.6">
       <c r="A35" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" ht="15.6">
       <c r="A38" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" ht="15.6">
       <c r="A41" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" ht="15.6">
       <c r="A44" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" ht="15.6">
       <c r="A47" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" ht="15.6">
       <c r="A50" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" ht="15.6">
       <c r="A53" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1" ht="15.6">
       <c r="A56" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1" ht="15.6">
       <c r="A59" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1" ht="15.6">
       <c r="A62" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1">
       <c r="A64" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="21.75" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:5" ht="21">
       <c r="A70" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="15.6">
       <c r="A74" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="15.6">
       <c r="A77" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="15.6">
       <c r="A78" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C80" s="12" t="s">
+    <row r="80" spans="1:5">
+      <c r="C80" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-    </row>
-    <row r="81" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+    </row>
+    <row r="81" spans="3:5" ht="15.6">
       <c r="C81" s="8" t="s">
         <v>87</v>
       </c>
@@ -1520,8 +1769,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="82" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="C82" s="9" t="s">
+    <row r="82" spans="3:5" ht="15.6">
+      <c r="C82" s="11" t="s">
         <v>90</v>
       </c>
       <c r="D82" s="7" t="s">
@@ -1531,8 +1780,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="C83" s="10"/>
+    <row r="83" spans="3:5" ht="15.6">
+      <c r="C83" s="12"/>
       <c r="D83" s="7" t="s">
         <v>93</v>
       </c>
@@ -1540,8 +1789,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="C84" s="10"/>
+    <row r="84" spans="3:5" ht="15.6">
+      <c r="C84" s="12"/>
       <c r="D84" s="7" t="s">
         <v>94</v>
       </c>
@@ -1549,8 +1798,8 @@
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="C85" s="11"/>
+    <row r="85" spans="3:5" ht="15.6">
+      <c r="C85" s="13"/>
       <c r="D85" s="7" t="s">
         <v>95</v>
       </c>
@@ -1558,8 +1807,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="86" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="C86" s="9" t="s">
+    <row r="86" spans="3:5" ht="15.6">
+      <c r="C86" s="11" t="s">
         <v>91</v>
       </c>
       <c r="D86" s="7" t="s">
@@ -1569,8 +1818,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="C87" s="10"/>
+    <row r="87" spans="3:5" ht="15.6">
+      <c r="C87" s="12"/>
       <c r="D87" s="7" t="s">
         <v>97</v>
       </c>
@@ -1578,8 +1827,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="88" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="C88" s="11"/>
+    <row r="88" spans="3:5" ht="15.6">
+      <c r="C88" s="13"/>
       <c r="D88" s="7" t="s">
         <v>98</v>
       </c>
@@ -1587,14 +1836,14 @@
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C90" s="12" t="s">
+    <row r="90" spans="3:5">
+      <c r="C90" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-    </row>
-    <row r="91" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D90" s="10"/>
+      <c r="E90" s="10"/>
+    </row>
+    <row r="91" spans="3:5" ht="15.6">
       <c r="C91" s="7" t="s">
         <v>3</v>
       </c>
@@ -1605,7 +1854,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="92" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:5" ht="15.6">
       <c r="C92" s="7" t="s">
         <v>107</v>
       </c>
@@ -1616,7 +1865,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="93" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:5" ht="15.6">
       <c r="C93" s="7" t="s">
         <v>110</v>
       </c>
@@ -1627,7 +1876,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="94" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:5" ht="15.6">
       <c r="C94" s="7" t="s">
         <v>113</v>
       </c>
@@ -1638,7 +1887,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="3:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:5" ht="15.6">
       <c r="C96" s="4" t="s">
         <v>116</v>
       </c>
@@ -1649,7 +1898,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="C97" s="4" t="s">
         <v>119</v>
       </c>
@@ -1660,7 +1909,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="15.6">
       <c r="C98" s="4" t="s">
         <v>119</v>
       </c>
@@ -1671,179 +1920,179 @@
         <v>123</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" ht="15.6">
       <c r="C99" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D99" s="13" t="s">
+      <c r="D99" s="4" t="s">
         <v>124</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="C100" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="4" t="s">
         <v>126</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A105" s="14" t="s">
+    <row r="105" spans="1:5" ht="17.399999999999999">
+      <c r="A105" s="9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="15.6">
       <c r="A109" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="15.6">
       <c r="A112" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="114" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1" ht="15.6">
       <c r="A114" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1" ht="15.6">
       <c r="A116" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1" ht="15.6">
       <c r="A118" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="119" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1" ht="15.6">
       <c r="A119" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1" ht="15.6">
       <c r="A121" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="123" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:1" ht="15.6">
       <c r="A123" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1">
       <c r="A124" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="127" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:1" ht="15.6">
       <c r="A127" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="128" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:1" ht="15.6">
       <c r="A128" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:1" ht="15.6">
       <c r="A129" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="130" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:1" ht="15.6">
       <c r="A130" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="131" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:1" ht="15.6">
       <c r="A131" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="132" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:1" ht="15.6">
       <c r="A132" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:1" ht="15.6">
       <c r="A133" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="134" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:1" ht="15.6">
       <c r="A134" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="135" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:1" ht="15.6">
       <c r="A135" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="136" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:1" ht="15.6">
       <c r="A136" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="137" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:1" ht="15.6">
       <c r="A137" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="139" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:1" ht="15.6">
       <c r="A139" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:1" ht="15.6">
       <c r="A140" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1">
       <c r="A141" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1">
       <c r="A142" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1">
       <c r="A143" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1">
       <c r="A144" t="s">
         <v>156</v>
       </c>
@@ -1864,17 +2113,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A7C180-FD00-4E0F-B89C-A62A7C6144AC}">
   <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1882,17 +2131,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1900,12 +2149,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1913,17 +2162,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="C35" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1931,17 +2180,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="C40" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="C41" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1949,7 +2198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -1957,12 +2206,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1970,22 +2219,22 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="C48" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
         <v>31</v>
       </c>
@@ -1993,7 +2242,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
         <v>32</v>
       </c>
@@ -2001,12 +2250,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2">
       <c r="A58" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>36</v>
       </c>
@@ -2019,4 +2268,370 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5F9465-11B7-43FE-9455-7EFCD5B4D61A}">
+  <dimension ref="A1:A88"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/English/语法.xlsx
+++ b/English/语法.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D77BDF7-99C8-4EAD-9EDA-77C100802449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C0D486-8834-4694-B2DF-508C821EC81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="词法加句法" sheetId="1" r:id="rId1"/>
     <sheet name="时态" sheetId="2" r:id="rId2"/>
     <sheet name="语法总结" sheetId="3" r:id="rId3"/>
+    <sheet name="过去分词" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="297">
   <si>
     <t>名词</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -952,6 +953,330 @@
   </si>
   <si>
     <t>必会3：主动/被动语态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动语态的核心结构是 be + 动词过去分词(done)，表达某事/物被执行的动作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动词原形及释义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>write</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去分词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wrote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>written</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>break</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>broken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chosen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承受/出生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>borne(承受) / born (出生)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>take</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>携带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>took</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>token</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>give</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给，赠送</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>given</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上升，升起</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>risen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eaten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忘记</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forgot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forgotten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谈话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spoke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spoken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>begin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>began</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>begun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>落下、掉落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fallen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>think</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>思考、认为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thought</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>find</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到、发现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>found</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保持、保存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kept</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>build</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建造</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>built</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The bridge 是建造动作的承受者，the government 为动作的发出者。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必会4：非谓语动词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非谓语动词主要有三种形式： to do(动词不定式)、doing (动名词/现在分词)和done(过去分词）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>形式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心含义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>done</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表目的、计划将来动作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动名词表活动、状态起名词作用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在分词表主动、进行起形容词/副词作用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表被动、完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He studies to pass CET-4.
+他为了通过英语四级考试学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>She enjoys reading English books.
+她爱读英语书。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The girl reading a book is Monica.
+读书的女孩是莫妮卡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seen from space, Earth is blue.
+从太空看去，地球是蓝色的。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1046,7 +1371,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1056,6 +1381,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1124,7 +1455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1135,6 +1466,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1147,8 +1480,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1752,11 +2100,11 @@
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
     </row>
     <row r="81" spans="3:5" ht="15.6">
       <c r="C81" s="8" t="s">
@@ -1770,7 +2118,7 @@
       </c>
     </row>
     <row r="82" spans="3:5" ht="15.6">
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D82" s="7" t="s">
@@ -1781,7 +2129,7 @@
       </c>
     </row>
     <row r="83" spans="3:5" ht="15.6">
-      <c r="C83" s="12"/>
+      <c r="C83" s="14"/>
       <c r="D83" s="7" t="s">
         <v>93</v>
       </c>
@@ -1790,7 +2138,7 @@
       </c>
     </row>
     <row r="84" spans="3:5" ht="15.6">
-      <c r="C84" s="12"/>
+      <c r="C84" s="14"/>
       <c r="D84" s="7" t="s">
         <v>94</v>
       </c>
@@ -1799,7 +2147,7 @@
       </c>
     </row>
     <row r="85" spans="3:5" ht="15.6">
-      <c r="C85" s="13"/>
+      <c r="C85" s="15"/>
       <c r="D85" s="7" t="s">
         <v>95</v>
       </c>
@@ -1808,7 +2156,7 @@
       </c>
     </row>
     <row r="86" spans="3:5" ht="15.6">
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D86" s="7" t="s">
@@ -1819,7 +2167,7 @@
       </c>
     </row>
     <row r="87" spans="3:5" ht="15.6">
-      <c r="C87" s="12"/>
+      <c r="C87" s="14"/>
       <c r="D87" s="7" t="s">
         <v>97</v>
       </c>
@@ -1828,7 +2176,7 @@
       </c>
     </row>
     <row r="88" spans="3:5" ht="15.6">
-      <c r="C88" s="13"/>
+      <c r="C88" s="15"/>
       <c r="D88" s="7" t="s">
         <v>98</v>
       </c>
@@ -1837,11 +2185,11 @@
       </c>
     </row>
     <row r="90" spans="3:5">
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
     </row>
     <row r="91" spans="3:5" ht="15.6">
       <c r="C91" s="7" t="s">
@@ -2272,8 +2620,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5F9465-11B7-43FE-9455-7EFCD5B4D61A}">
-  <dimension ref="A1:A88"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="35.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -2351,7 +2703,7 @@
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="10" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2406,7 +2758,7 @@
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2456,7 +2808,7 @@
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="11" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2491,7 +2843,7 @@
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="11" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2521,7 +2873,7 @@
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2571,7 +2923,7 @@
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2630,7 +2982,344 @@
         <v>216</v>
       </c>
     </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C113" s="21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="55.8" customHeight="1">
+      <c r="A114" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="39" customHeight="1">
+      <c r="A115" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="41.4">
+      <c r="A116" s="20"/>
+      <c r="B116" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="36.6" customHeight="1">
+      <c r="A117" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>296</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A115:A116"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD78CA20-BA15-452F-9BC1-E73108303147}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>280</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/English/语法.xlsx
+++ b/English/语法.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C0D486-8834-4694-B2DF-508C821EC81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72886EC3-060A-4DD4-96E3-0A5B3920CE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="16656" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="词法加句法" sheetId="1" r:id="rId1"/>
     <sheet name="时态" sheetId="2" r:id="rId2"/>
     <sheet name="语法总结" sheetId="3" r:id="rId3"/>
     <sheet name="过去分词" sheetId="4" r:id="rId4"/>
+    <sheet name="单词" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="442">
   <si>
     <t>名词</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1277,6 +1278,575 @@
   <si>
     <t>Seen from space, Earth is blue.
 从太空看去，地球是蓝色的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diligent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勤奋的、刻苦的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+快的，迅速的。要害，核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>understand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理解、明白</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complicate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复杂的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concept</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>概念、思想</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>become</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成为、变成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>future</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建议、忠告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丢失、掉落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>more</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更多</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>关于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>event</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>农民</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>important</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>been</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>borrow</t>
+  </si>
+  <si>
+    <t>借</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过、及格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>child</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孩子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>park</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公园</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>practice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>during</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在...期间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lent</t>
+  </si>
+  <si>
+    <t>借、借出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fascinate</t>
+  </si>
+  <si>
+    <t>入迷、迷人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>来源、源头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无休止的、无尽的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>决定、抉择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>much</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很多、更加、非常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>some</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一些</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>friendly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>友好地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量、能力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>learn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rich</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>富有的、富饶的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>should</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应该</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>traffic</t>
+  </si>
+  <si>
+    <t>交通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>告诉、说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金钱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>usual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通常的、惯用的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早餐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lunch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>午餐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dinner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚餐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>south</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>winter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bird</t>
+  </si>
+  <si>
+    <t>鸟、鸟类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enough</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>足够的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成、结局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>favorite</t>
+  </si>
+  <si>
+    <t>最喜欢的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>激发、兴奋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无用的、不行的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laptop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>repair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>笔记本电脑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修理、维修</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>父母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>brother</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兄弟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clean</t>
+  </si>
+  <si>
+    <t>清洁、清理、清洁的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>书桌、办公桌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>院子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汤、羹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>special</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加入、连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>large</t>
+  </si>
+  <si>
+    <t>大量的、大的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spend</t>
+  </si>
+  <si>
+    <t>花费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烹饪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knife</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>叉子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>床</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lying</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>躺、说谎</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1455,7 +2025,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1468,6 +2038,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1480,23 +2060,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2100,11 +2669,11 @@
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
     </row>
     <row r="81" spans="3:5" ht="15.6">
       <c r="C81" s="8" t="s">
@@ -2118,7 +2687,7 @@
       </c>
     </row>
     <row r="82" spans="3:5" ht="15.6">
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D82" s="7" t="s">
@@ -2129,7 +2698,7 @@
       </c>
     </row>
     <row r="83" spans="3:5" ht="15.6">
-      <c r="C83" s="14"/>
+      <c r="C83" s="18"/>
       <c r="D83" s="7" t="s">
         <v>93</v>
       </c>
@@ -2138,7 +2707,7 @@
       </c>
     </row>
     <row r="84" spans="3:5" ht="15.6">
-      <c r="C84" s="14"/>
+      <c r="C84" s="18"/>
       <c r="D84" s="7" t="s">
         <v>94</v>
       </c>
@@ -2147,7 +2716,7 @@
       </c>
     </row>
     <row r="85" spans="3:5" ht="15.6">
-      <c r="C85" s="15"/>
+      <c r="C85" s="19"/>
       <c r="D85" s="7" t="s">
         <v>95</v>
       </c>
@@ -2156,7 +2725,7 @@
       </c>
     </row>
     <row r="86" spans="3:5" ht="15.6">
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="17" t="s">
         <v>91</v>
       </c>
       <c r="D86" s="7" t="s">
@@ -2167,7 +2736,7 @@
       </c>
     </row>
     <row r="87" spans="3:5" ht="15.6">
-      <c r="C87" s="14"/>
+      <c r="C87" s="18"/>
       <c r="D87" s="7" t="s">
         <v>97</v>
       </c>
@@ -2176,7 +2745,7 @@
       </c>
     </row>
     <row r="88" spans="3:5" ht="15.6">
-      <c r="C88" s="15"/>
+      <c r="C88" s="19"/>
       <c r="D88" s="7" t="s">
         <v>98</v>
       </c>
@@ -2185,11 +2754,11 @@
       </c>
     </row>
     <row r="90" spans="3:5">
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
     </row>
     <row r="91" spans="3:5" ht="15.6">
       <c r="C91" s="7" t="s">
@@ -3008,24 +3577,24 @@
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="16" t="s">
+      <c r="A113" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B113" s="16" t="s">
+      <c r="B113" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" s="15" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="55.8" customHeight="1">
-      <c r="A114" s="19" t="s">
+      <c r="A114" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="B114" s="19" t="s">
+      <c r="B114" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="C114" s="19" t="s">
+      <c r="C114" s="14" t="s">
         <v>293</v>
       </c>
     </row>
@@ -3033,30 +3602,30 @@
       <c r="A115" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="B115" s="19" t="s">
+      <c r="B115" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="C115" s="19" t="s">
+      <c r="C115" s="14" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="41.4">
       <c r="A116" s="20"/>
-      <c r="B116" s="19" t="s">
+      <c r="B116" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="C116" s="19" t="s">
+      <c r="C116" s="14" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="36.6" customHeight="1">
-      <c r="A117" s="19" t="s">
+      <c r="A117" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B117" s="19" t="s">
+      <c r="B117" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="C117" s="19" t="s">
+      <c r="C117" s="14" t="s">
         <v>296</v>
       </c>
     </row>
@@ -3081,238 +3650,238 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="18" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="13" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="12" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="12" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="12" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="12" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="12" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="12" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="12" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="12" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="12" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="12" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="12" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="12" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="12" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="12" t="s">
         <v>280</v>
       </c>
     </row>
@@ -3323,4 +3892,626 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E206E81E-A0E1-4FCC-BDBC-CD290783D42D}">
+  <dimension ref="A1:B76"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B13" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>322</v>
+      </c>
+      <c r="B14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>324</v>
+      </c>
+      <c r="B15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>329</v>
+      </c>
+      <c r="B18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>331</v>
+      </c>
+      <c r="B19" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>335</v>
+      </c>
+      <c r="B21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>339</v>
+      </c>
+      <c r="B23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>341</v>
+      </c>
+      <c r="B24" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>343</v>
+      </c>
+      <c r="B25" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>345</v>
+      </c>
+      <c r="B26" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>347</v>
+      </c>
+      <c r="B27" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>349</v>
+      </c>
+      <c r="B28" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>351</v>
+      </c>
+      <c r="B29" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>354</v>
+      </c>
+      <c r="B31" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>356</v>
+      </c>
+      <c r="B32" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>358</v>
+      </c>
+      <c r="B33" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>360</v>
+      </c>
+      <c r="B34" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>362</v>
+      </c>
+      <c r="B35" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>364</v>
+      </c>
+      <c r="B36" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>366</v>
+      </c>
+      <c r="B37" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>368</v>
+      </c>
+      <c r="B38" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>370</v>
+      </c>
+      <c r="B39" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>374</v>
+      </c>
+      <c r="B42" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>376</v>
+      </c>
+      <c r="B43" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>379</v>
+      </c>
+      <c r="B45" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>381</v>
+      </c>
+      <c r="B46" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>383</v>
+      </c>
+      <c r="B47" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>385</v>
+      </c>
+      <c r="B48" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>387</v>
+      </c>
+      <c r="B49" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>388</v>
+      </c>
+      <c r="B50" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>390</v>
+      </c>
+      <c r="B51" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>392</v>
+      </c>
+      <c r="B52" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>394</v>
+      </c>
+      <c r="B53" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>396</v>
+      </c>
+      <c r="B54" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>398</v>
+      </c>
+      <c r="B55" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>400</v>
+      </c>
+      <c r="B56" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>402</v>
+      </c>
+      <c r="B57" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B58" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>406</v>
+      </c>
+      <c r="B59" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>407</v>
+      </c>
+      <c r="B60" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>410</v>
+      </c>
+      <c r="B61" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>412</v>
+      </c>
+      <c r="B62" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>414</v>
+      </c>
+      <c r="B63" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>416</v>
+      </c>
+      <c r="B64" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>418</v>
+      </c>
+      <c r="B65" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>420</v>
+      </c>
+      <c r="B66" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>422</v>
+      </c>
+      <c r="B67" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>424</v>
+      </c>
+      <c r="B68" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>426</v>
+      </c>
+      <c r="B69" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>428</v>
+      </c>
+      <c r="B70" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>430</v>
+      </c>
+      <c r="B71" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>432</v>
+      </c>
+      <c r="B72" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>434</v>
+      </c>
+      <c r="B73" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>436</v>
+      </c>
+      <c r="B74" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>438</v>
+      </c>
+      <c r="B75" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>440</v>
+      </c>
+      <c r="B76" t="s">
+        <v>441</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>